--- a/BWI/bestwine_output/bestwine_Iceland.xlsx
+++ b/BWI/bestwine_output/bestwine_Iceland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5561,6 +5561,208 @@
       </c>
       <c r="AA49" s="2" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Sg Veitingar Ehf.</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Sg Veitingar Ehf.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>50174</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Hafnarfjörður</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Hafnarfjarðarkaupstaður</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Borgahella 3</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://nammi.is</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>info@nammi.is</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>+354 588 5577</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nammi-is/</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/nammi.is/</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nammi.is.iceland/</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>Sófus Gústavsson</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sofusgustavsson/?originalSubdomain=is</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Heinemann Travel Retail Iceland ehf.</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Ísland Duty Free</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>42271</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Keflavík</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Keflavík</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>235 Keflavíkurflugvöllu</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dutyfree.is</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>dutyfree@dutyfree.is</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>+354 425 0410</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>6112042130</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iislanddutyfree</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/island.dutyfree</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>Thorgerdur Thrainsdottir</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thorgerdur-thrainsdottir-097602180/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Iceland.xlsx
+++ b/BWI/bestwine_output/bestwine_Iceland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5763,6 +5763,95 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Vinbudin</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Vinbudin</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>41177</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Reykjavík</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Reykjavíkurborg</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2 Stuðlaháls</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinbudin.is</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>vinbudin@vinbudin.is</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>+354 560 7700</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>4101694369</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinbudin.is/</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr"/>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
